--- a/06-Gap-Assessment/ISO-27001-Gap-Assessment.xlsx
+++ b/06-Gap-Assessment/ISO-27001-Gap-Assessment.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="58">
   <si>
-    <t xml:space="preserve">Simulated portfolio project - SecurePay Technologies Pvt. Ltd. is fictional. Not a certification claim. Rows marked '(added)' extend the brief to cover risks R-013 and R-018.</t>
+    <t xml:space="preserve">Simulated portfolio project - HawkPay Technologies Pvt. Ltd. is fictional. Not a certification claim. Rows marked '(added)' extend the brief to cover risks R-013 and R-018.</t>
   </si>
   <si>
     <t xml:space="preserve">Control Area</t>
